--- a/hardware/bom/Bill of Materials-EEG_Trigger.xlsx
+++ b/hardware/bom/Bill of Materials-EEG_Trigger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\EEG_Trigger\Project Outputs for EEG_Trigger\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EE38362-7D38-4277-9AB8-7C72EDF65EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCD5AEE9-326D-4BE7-8F77-2C55B0139B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{A8AC91FA-3DCD-42E3-9B9B-0B04D1EEF43B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{C70F5BB8-9973-497C-A946-880EA3E80774}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-EEG_Trigger" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="180">
   <si>
     <t>Comment</t>
   </si>
@@ -80,7 +80,7 @@
     <t>CAP CER 0.1UF 50V X7R 0402</t>
   </si>
   <si>
-    <t>C1, C3, C5, C7, C8, C9, C11, C14</t>
+    <t>C1, C3, C5, C7, C8, C9, C11, C14, C18</t>
   </si>
   <si>
     <t>CAPC1005X65N</t>
@@ -98,13 +98,52 @@
     <t>Arrow Electronics</t>
   </si>
   <si>
+    <t>4.7uF, 16V</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 16V X5R 0402</t>
+  </si>
+  <si>
+    <t>C2, C6, C17</t>
+  </si>
+  <si>
+    <t>CL05A475MO5NUNC</t>
+  </si>
+  <si>
+    <t>C318563</t>
+  </si>
+  <si>
+    <t>Avnet</t>
+  </si>
+  <si>
+    <t>10uF 0805</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 10V 10uF X7R 0805 10% AEC-Q200</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>CAPC2012X88N</t>
+  </si>
+  <si>
+    <t>C0805C106K8RACAUTO</t>
+  </si>
+  <si>
+    <t>C696369</t>
+  </si>
+  <si>
+    <t>KEMET</t>
+  </si>
+  <si>
     <t>1uF, 35V</t>
   </si>
   <si>
     <t>CAP CER 1UF 35V X5R 0402</t>
   </si>
   <si>
-    <t>C2, C10, C15, C16</t>
+    <t>C10, C15, C16</t>
   </si>
   <si>
     <t>CL05A105KL5NRNC</t>
@@ -113,27 +152,6 @@
     <t>C307413</t>
   </si>
   <si>
-    <t>10uF 0805</t>
-  </si>
-  <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 10V 10uF X7R 0805 10% AEC-Q200</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>CAPC2012X88N</t>
-  </si>
-  <si>
-    <t>C0805C106K8RACAUTO</t>
-  </si>
-  <si>
-    <t>C696369</t>
-  </si>
-  <si>
-    <t>KEMET</t>
-  </si>
-  <si>
     <t>22pF</t>
   </si>
   <si>
@@ -155,24 +173,6 @@
     <t>2773393</t>
   </si>
   <si>
-    <t>4.7uF, 16V</t>
-  </si>
-  <si>
-    <t>CAP CER 4.7UF 16V X5R 0402</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>CL05A475MO5NUNC</t>
-  </si>
-  <si>
-    <t>C318563</t>
-  </si>
-  <si>
-    <t>Avnet</t>
-  </si>
-  <si>
     <t>AQ3045-01ETG</t>
   </si>
   <si>
@@ -371,7 +371,7 @@
     <t>RES 10K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>R8</t>
+    <t>R8, R14</t>
   </si>
   <si>
     <t>SR0402FR-0710KL</t>
@@ -401,13 +401,13 @@
     <t>7334493</t>
   </si>
   <si>
-    <t>1K</t>
+    <t>1K, 1kΩ</t>
   </si>
   <si>
     <t>RES 1K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>R10, R27, R28</t>
+    <t>R10, R11, R16, R27, R28</t>
   </si>
   <si>
     <t>RC0402FR-071KL</t>
@@ -417,6 +417,63 @@
   </si>
   <si>
     <t>2421889</t>
+  </si>
+  <si>
+    <t>22.1K</t>
+  </si>
+  <si>
+    <t>22.1 kOhms ±1% 0.125W, 1/8W Chip Resistor 0805 (2012 Metric) Moisture Resistant Thick Film</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>RESC2012X60N</t>
+  </si>
+  <si>
+    <t>RC0805FR-0722K1L</t>
+  </si>
+  <si>
+    <t>C273840</t>
+  </si>
+  <si>
+    <t>DigiKey</t>
+  </si>
+  <si>
+    <t>311-22.1KCRDKR-ND</t>
+  </si>
+  <si>
+    <t>47.5K</t>
+  </si>
+  <si>
+    <t>47.5 kOhms ±1% 0.063W, 1/16W Chip Resistor 0402 (1005 Metric) Moisture Resistant Thick Film</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>RC0402FR-0747K5L</t>
+  </si>
+  <si>
+    <t>C137974</t>
+  </si>
+  <si>
+    <t>311-47.5KLRCT-ND</t>
+  </si>
+  <si>
+    <t>20kΩ 0603</t>
+  </si>
+  <si>
+    <t>20 kOhms ±1% 0.1W, 1/10W Chip Resistor 0603 (1608 Metric) Moisture Resistant Thick Film</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>RC0603FR-0720KL</t>
+  </si>
+  <si>
+    <t>C105575</t>
   </si>
   <si>
     <t>CP2102N</t>
@@ -917,8 +974,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219604BC-2E35-4AA7-B199-65E83289FF90}">
-  <dimension ref="A1:K23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{170614B2-DEA3-49B2-83E6-9FE9CA55EB63}">
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="6" width="18.81640625" customWidth="1"/>
@@ -977,7 +1034,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>16</v>
@@ -1012,7 +1069,7 @@
         <v>22</v>
       </c>
       <c r="F3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>23</v>
@@ -1024,7 +1081,7 @@
         <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>22</v>
@@ -1032,107 +1089,107 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -1164,7 +1221,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>50</v>
@@ -1304,7 +1361,7 @@
         <v>78</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>81</v>
@@ -1339,7 +1396,7 @@
         <v>85</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>87</v>
@@ -1409,7 +1466,7 @@
         <v>99</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>101</v>
@@ -1444,7 +1501,7 @@
         <v>105</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>107</v>
@@ -1467,7 +1524,7 @@
         <v>111</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>112</v>
@@ -1537,7 +1594,7 @@
         <v>123</v>
       </c>
       <c r="F18" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>124</v>
@@ -1549,7 +1606,7 @@
         <v>123</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>125</v>
@@ -1578,156 +1635,261 @@
         <v>131</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>130</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="I22" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F23" s="1">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>158</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
